--- a/docs/demos/correos/ExamLab-Usuarios-Demo.xlsx
+++ b/docs/demos/correos/ExamLab-Usuarios-Demo.xlsx
@@ -112,7 +112,11 @@
       </c>
       <c r="H2"/>
       <c r="I2"/>
-      <c r="J2"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -152,7 +156,11 @@
       </c>
       <c r="H3"/>
       <c r="I3"/>
-      <c r="J3"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -192,7 +200,11 @@
       </c>
       <c r="H4"/>
       <c r="I4"/>
-      <c r="J4"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -232,7 +244,11 @@
       </c>
       <c r="H5"/>
       <c r="I5"/>
-      <c r="J5"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -272,7 +288,11 @@
       </c>
       <c r="H6"/>
       <c r="I6"/>
-      <c r="J6"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/docs/demos/correos/ExamLab-Usuarios-Demo.xlsx
+++ b/docs/demos/correos/ExamLab-Usuarios-Demo.xlsx
@@ -97,7 +97,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docente</t>
+          <t xml:space="preserve">Docente + Estudiante</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -114,7 +114,7 @@
       <c r="I2"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
         </is>
       </c>
     </row>
@@ -141,7 +141,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docente</t>
+          <t xml:space="preserve">Docente + Estudiante</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -158,7 +158,7 @@
       <c r="I3"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
         </is>
       </c>
     </row>
@@ -185,7 +185,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docente</t>
+          <t xml:space="preserve">Docente + Estudiante</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -202,7 +202,7 @@
       <c r="I4"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
         </is>
       </c>
     </row>
@@ -229,7 +229,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docente</t>
+          <t xml:space="preserve">Docente + Estudiante</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -246,7 +246,7 @@
       <c r="I5"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
         </is>
       </c>
     </row>
@@ -273,7 +273,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docente</t>
+          <t xml:space="preserve">Docente + Estudiante</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -290,7 +290,7 @@
       <c r="I6"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma.</t>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
         </is>
       </c>
     </row>

--- a/docs/demos/correos/ExamLab-Usuarios-Demo.xlsx
+++ b/docs/demos/correos/ExamLab-Usuarios-Demo.xlsx
@@ -294,6 +294,1986 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente6@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente7@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente8@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente9@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente10@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente11@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente12@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente13@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente14@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente15@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente16@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente17@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente18@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente19@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente20@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente21@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente22@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente23@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente24@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente25@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente26@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente27@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente28@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente29@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente30@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente31@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente32@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente33@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 34</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente34@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente35@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 36</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente36@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 37</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente37@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 38</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente38@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente39@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 40</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente40@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 41</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente41@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 42</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente42@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente43@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 44</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente44@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente45@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 46</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente46@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 47</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente47@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente48@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 49</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente49@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente Demo 50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docente50@demo-examlab.co</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamlabDemo2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docente + Estudiante</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExamLab Demo</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://examlab.lovable.app/auth</t>
+        </is>
+      </c>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta de demo. Al iniciar sesión, selecciona la institución "ExamLab Demo". El espacio empieza vacío: crea tu propio curso para empezar y usa la IA para generar exámenes/talleres (corre al instante). No incluye estudiantes (la matrícula la hace un administrador), así que el ciclo completo de calificación de entregas reales se ve en los videos demo, no en esta cuenta. La contraseña es genérica y no caduca al primer ingreso. Si la IA falla puntualmente, suele ser disponibilidad del modelo (es una demo): espera unos minutos y reintenta — no es un error de la plataforma. La cuenta tiene dos roles (Docente y Estudiante): cambia con el selector arriba del menú para ver ambas vistas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>